--- a/data/raw/inventory/Week 28/Nexlev/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 28/Nexlev/Seller FBA Inventory (SP-API).xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,82 +417,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>ASIN</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>afn_fulfillable_quantity</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>afn_inbound_working_quantity</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>afn_inbound_shipped_quantity</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>afn_inbound_receiving_quantity</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>afn_reserved_quantity</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>afn_total_quantity</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>afn_unsellable_quantity</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>afn_researching_quantity</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Seller Account</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>SnapshotDate</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Week</t>
         </is>
@@ -1090,10 +1078,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="F11" t="n">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1105,10 +1093,10 @@
         <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1152,10 +1140,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="F12" t="n">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="G12" t="n">
         <v>90</v>
@@ -1167,13 +1155,13 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K12" t="n">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="L12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1524,7 +1512,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F18" t="n">
         <v>31</v>
@@ -1539,10 +1527,10 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K18" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L18" t="n">
         <v>12</v>
@@ -1589,7 +1577,7 @@
         <v>223</v>
       </c>
       <c r="F19" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G19" t="n">
         <v>10</v>
@@ -1601,7 +1589,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K19" t="n">
         <v>224</v>
@@ -1651,7 +1639,7 @@
         <v>153</v>
       </c>
       <c r="F20" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1663,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K20" t="n">
         <v>156</v>
@@ -1775,7 +1763,7 @@
         <v>88</v>
       </c>
       <c r="F22" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1787,7 +1775,7 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>88</v>
@@ -1899,7 +1887,7 @@
         <v>24</v>
       </c>
       <c r="F24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1911,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>24</v>
@@ -2519,7 +2507,7 @@
         <v>273</v>
       </c>
       <c r="F34" t="n">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -2531,7 +2519,7 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K34" t="n">
         <v>275</v>
@@ -2581,7 +2569,7 @@
         <v>165</v>
       </c>
       <c r="F35" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -2593,7 +2581,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K35" t="n">
         <v>165</v>
@@ -2767,7 +2755,7 @@
         <v>151</v>
       </c>
       <c r="F38" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G38" t="n">
         <v>60</v>
@@ -2779,7 +2767,7 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K38" t="n">
         <v>152</v>
@@ -2888,7 +2876,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F40" t="n">
         <v>33</v>
@@ -2903,10 +2891,10 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K40" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L40" t="n">
         <v>2</v>
@@ -2950,10 +2938,10 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F41" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G41" t="n">
         <v>72</v>
@@ -2965,10 +2953,10 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K41" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="L41" t="n">
         <v>4</v>
@@ -3136,25 +3124,25 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="F44" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G44" t="n">
-        <v>124</v>
+        <v>22</v>
       </c>
       <c r="H44" t="n">
-        <v>198</v>
+        <v>300</v>
       </c>
       <c r="I44" t="n">
         <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K44" t="n">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="L44" t="n">
         <v>26</v>
@@ -3201,7 +3189,7 @@
         <v>59</v>
       </c>
       <c r="F45" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G45" t="n">
         <v>20</v>
@@ -3213,7 +3201,7 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K45" t="n">
         <v>59</v>
@@ -3387,7 +3375,7 @@
         <v>28</v>
       </c>
       <c r="F48" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -3399,7 +3387,7 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K48" t="n">
         <v>28</v>
@@ -3449,7 +3437,7 @@
         <v>28</v>
       </c>
       <c r="F49" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -3461,7 +3449,7 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K49" t="n">
         <v>28</v>
@@ -3759,7 +3747,7 @@
         <v>34</v>
       </c>
       <c r="F54" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -3771,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
         <v>34</v>
@@ -4252,7 +4240,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F62" t="n">
         <v>226</v>
@@ -4267,10 +4255,10 @@
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K62" t="n">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="L62" t="n">
         <v>3</v>
@@ -4441,25 +4429,25 @@
         <v>432</v>
       </c>
       <c r="F65" t="n">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="G65" t="n">
-        <v>162</v>
+        <v>62</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="K65" t="n">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="L65" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M65" t="n">
         <v>2</v>
@@ -4562,10 +4550,10 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F67" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -4580,7 +4568,7 @@
         <v>6</v>
       </c>
       <c r="K67" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -4704,10 +4692,10 @@
         <v>2</v>
       </c>
       <c r="K69" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
@@ -4813,7 +4801,7 @@
         <v>16</v>
       </c>
       <c r="F71" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -4825,7 +4813,7 @@
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K71" t="n">
         <v>16</v>
@@ -4996,10 +4984,10 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="F74" t="n">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="G74" t="n">
         <v>90</v>
@@ -5011,10 +4999,10 @@
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="K74" t="n">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="L74" t="n">
         <v>23</v>
@@ -5247,7 +5235,7 @@
         <v>35</v>
       </c>
       <c r="F78" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -5259,7 +5247,7 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K78" t="n">
         <v>35</v>
@@ -5368,7 +5356,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F80" t="n">
         <v>28</v>
@@ -5383,10 +5371,10 @@
         <v>1</v>
       </c>
       <c r="J80" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K80" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L80" t="n">
         <v>9</v>
@@ -5867,7 +5855,7 @@
         <v>170</v>
       </c>
       <c r="F88" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -5879,7 +5867,7 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K88" t="n">
         <v>170</v>
@@ -6316,10 +6304,10 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M95" t="n">
         <v>0</v>
@@ -6685,7 +6673,7 @@
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K101" t="n">
         <v>126</v>
@@ -6694,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -6750,10 +6738,10 @@
         <v>4</v>
       </c>
       <c r="K102" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M102" t="n">
         <v>1</v>
@@ -6918,7 +6906,7 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F105" t="n">
         <v>33</v>
@@ -6933,10 +6921,10 @@
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K105" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L105" t="n">
         <v>0</v>
@@ -7104,25 +7092,25 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F108" t="n">
         <v>42</v>
       </c>
       <c r="G108" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>102</v>
+        <v>166</v>
       </c>
       <c r="I108" t="n">
         <v>0</v>
       </c>
       <c r="J108" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K108" t="n">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="L108" t="n">
         <v>6</v>
@@ -7290,7 +7278,7 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F111" t="n">
         <v>35</v>
@@ -7305,10 +7293,10 @@
         <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L111" t="n">
         <v>0</v>
@@ -7352,10 +7340,10 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F112" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -7370,7 +7358,7 @@
         <v>31</v>
       </c>
       <c r="K112" t="n">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
@@ -7482,10 +7470,10 @@
         <v>18</v>
       </c>
       <c r="G114" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="I114" t="n">
         <v>0</v>
@@ -8285,7 +8273,7 @@
         <v>111</v>
       </c>
       <c r="F127" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -8297,7 +8285,7 @@
         <v>0</v>
       </c>
       <c r="J127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K127" t="n">
         <v>112</v>
@@ -8406,7 +8394,7 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F129" t="n">
         <v>3</v>
@@ -8421,10 +8409,10 @@
         <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K129" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L129" t="n">
         <v>0</v>
@@ -8716,10 +8704,10 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F134" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -8731,10 +8719,10 @@
         <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K134" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L134" t="n">
         <v>2</v>
@@ -11196,10 +11184,10 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F174" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G174" t="n">
         <v>30</v>
@@ -11211,10 +11199,10 @@
         <v>1</v>
       </c>
       <c r="J174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K174" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="L174" t="n">
         <v>3</v>
@@ -12064,7 +12052,7 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F188" t="n">
         <v>22</v>
@@ -12079,10 +12067,10 @@
         <v>0</v>
       </c>
       <c r="J188" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K188" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L188" t="n">
         <v>0</v>

--- a/data/raw/inventory/Week 28/Nexlev/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 28/Nexlev/Seller FBA Inventory (SP-API).xlsx
@@ -1078,13 +1078,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>388</v>
+        <v>431</v>
       </c>
       <c r="F11" t="n">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H11" t="n">
         <v>48</v>
@@ -1093,10 +1093,10 @@
         <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K11" t="n">
-        <v>388</v>
+        <v>431</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1140,13 +1140,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>676</v>
+        <v>696</v>
       </c>
       <c r="F12" t="n">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="G12" t="n">
-        <v>90</v>
+        <v>126</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1155,13 +1155,13 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K12" t="n">
-        <v>688</v>
+        <v>706</v>
       </c>
       <c r="L12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
         <v>2</v>
@@ -1403,10 +1403,10 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="F18" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1527,13 +1527,13 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K18" t="n">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="L18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M18" t="n">
         <v>4</v>
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F20" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1651,10 +1651,10 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="L20" t="n">
         <v>3</v>
@@ -1701,7 +1701,7 @@
         <v>227</v>
       </c>
       <c r="F21" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1713,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>227</v>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F22" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1778,7 +1778,7 @@
         <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -1822,10 +1822,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F23" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1840,7 +1840,7 @@
         <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2197,7 +2197,7 @@
         <v>186</v>
       </c>
       <c r="F29" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K29" t="n">
         <v>186</v>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F33" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -2460,7 +2460,7 @@
         <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F34" t="n">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -2519,10 +2519,10 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K34" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L34" t="n">
         <v>2</v>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F35" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -2581,10 +2581,10 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K35" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -2628,10 +2628,10 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F36" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F38" t="n">
         <v>88</v>
@@ -2767,13 +2767,13 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K38" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -2876,7 +2876,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F40" t="n">
         <v>33</v>
@@ -2891,13 +2891,13 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K40" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M40" t="n">
         <v>1</v>
@@ -2938,10 +2938,10 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="F41" t="n">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="G41" t="n">
         <v>72</v>
@@ -2953,10 +2953,10 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K41" t="n">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="L41" t="n">
         <v>4</v>
@@ -3000,25 +3000,25 @@
         </is>
       </c>
       <c r="E42" t="n">
+        <v>142</v>
+      </c>
+      <c r="F42" t="n">
+        <v>141</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" t="n">
         <v>143</v>
-      </c>
-      <c r="F42" t="n">
-        <v>143</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="n">
-        <v>144</v>
       </c>
       <c r="L42" t="n">
         <v>1</v>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F43" t="n">
         <v>105</v>
@@ -3077,10 +3077,10 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -3124,10 +3124,10 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="F44" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="G44" t="n">
         <v>22</v>
@@ -3139,13 +3139,13 @@
         <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K44" t="n">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="L44" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -3186,10 +3186,10 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F45" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G45" t="n">
         <v>20</v>
@@ -3201,10 +3201,10 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K45" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -3248,10 +3248,10 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -3266,7 +3266,7 @@
         <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -3372,7 +3372,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F48" t="n">
         <v>23</v>
@@ -3387,10 +3387,10 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K48" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -3561,7 +3561,7 @@
         <v>10</v>
       </c>
       <c r="F51" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -3573,7 +3573,7 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
         <v>10</v>
@@ -3620,7 +3620,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F52" t="n">
         <v>1</v>
@@ -3635,10 +3635,10 @@
         <v>0</v>
       </c>
       <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
         <v>1</v>
-      </c>
-      <c r="K52" t="n">
-        <v>2</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -3744,10 +3744,10 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F54" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -3762,7 +3762,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -4240,13 +4240,13 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="F62" t="n">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="G62" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="H62" t="n">
         <v>34</v>
@@ -4255,13 +4255,13 @@
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K62" t="n">
-        <v>338</v>
+        <v>359</v>
       </c>
       <c r="L62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
@@ -4382,10 +4382,10 @@
         <v>1</v>
       </c>
       <c r="K64" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
         <v>0</v>
@@ -4426,10 +4426,10 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="F65" t="n">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="G65" t="n">
         <v>62</v>
@@ -4444,10 +4444,10 @@
         <v>33</v>
       </c>
       <c r="K65" t="n">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="L65" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M65" t="n">
         <v>2</v>
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F67" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -4565,10 +4565,10 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K67" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -4798,7 +4798,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F71" t="n">
         <v>15</v>
@@ -4813,10 +4813,10 @@
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
@@ -4984,10 +4984,10 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>529</v>
+        <v>500</v>
       </c>
       <c r="F74" t="n">
-        <v>396</v>
+        <v>370</v>
       </c>
       <c r="G74" t="n">
         <v>90</v>
@@ -4999,13 +4999,13 @@
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="K74" t="n">
-        <v>552</v>
+        <v>521</v>
       </c>
       <c r="L74" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -5111,7 +5111,7 @@
         <v>50</v>
       </c>
       <c r="F76" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -5123,7 +5123,7 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K76" t="n">
         <v>50</v>
@@ -5232,7 +5232,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F78" t="n">
         <v>34</v>
@@ -5247,10 +5247,10 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -5356,10 +5356,10 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F80" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -5368,16 +5368,16 @@
         <v>10</v>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="K80" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="L80" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F82" t="n">
         <v>220</v>
@@ -5495,10 +5495,10 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K82" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L82" t="n">
         <v>2</v>
@@ -5746,10 +5746,10 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L86" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
@@ -5855,7 +5855,7 @@
         <v>170</v>
       </c>
       <c r="F88" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -5867,7 +5867,7 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
         <v>170</v>
@@ -6165,7 +6165,7 @@
         <v>2</v>
       </c>
       <c r="F93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -6177,7 +6177,7 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K93" t="n">
         <v>2</v>
@@ -6224,25 +6224,25 @@
         </is>
       </c>
       <c r="E94" t="n">
+        <v>10</v>
+      </c>
+      <c r="F94" t="n">
+        <v>9</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
         <v>11</v>
-      </c>
-      <c r="F94" t="n">
-        <v>10</v>
-      </c>
-      <c r="G94" t="n">
-        <v>0</v>
-      </c>
-      <c r="H94" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94" t="n">
-        <v>0</v>
-      </c>
-      <c r="J94" t="n">
-        <v>0</v>
-      </c>
-      <c r="K94" t="n">
-        <v>12</v>
       </c>
       <c r="L94" t="n">
         <v>1</v>
@@ -6289,7 +6289,7 @@
         <v>24</v>
       </c>
       <c r="F95" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -6301,7 +6301,7 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K95" t="n">
         <v>25</v>
@@ -6366,10 +6366,10 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L96" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M96" t="n">
         <v>0</v>
@@ -6720,10 +6720,10 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F102" t="n">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="G102" t="n">
         <v>8</v>
@@ -6735,10 +6735,10 @@
         <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K102" t="n">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="L102" t="n">
         <v>3</v>
@@ -6782,10 +6782,10 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="F103" t="n">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -6800,7 +6800,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="L103" t="n">
         <v>0</v>
@@ -6847,7 +6847,7 @@
         <v>25</v>
       </c>
       <c r="F104" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -6859,7 +6859,7 @@
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K104" t="n">
         <v>25</v>
@@ -6906,10 +6906,10 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F105" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -6921,10 +6921,10 @@
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K105" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L105" t="n">
         <v>0</v>
@@ -6986,10 +6986,10 @@
         <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
         <v>0</v>
@@ -7092,10 +7092,10 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="F108" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -7107,10 +7107,10 @@
         <v>0</v>
       </c>
       <c r="J108" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K108" t="n">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="L108" t="n">
         <v>6</v>
@@ -7154,13 +7154,13 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="F109" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -7169,10 +7169,10 @@
         <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K109" t="n">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
@@ -7278,13 +7278,13 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="F111" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -7296,7 +7296,7 @@
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="L111" t="n">
         <v>0</v>
@@ -7340,10 +7340,10 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="F112" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -7355,10 +7355,10 @@
         <v>0</v>
       </c>
       <c r="J112" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="K112" t="n">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
@@ -7402,10 +7402,10 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F113" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -7417,10 +7417,10 @@
         <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
@@ -7464,10 +7464,10 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F114" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -7479,13 +7479,13 @@
         <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K114" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L114" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M114" t="n">
         <v>0</v>
@@ -8211,7 +8211,7 @@
         <v>20</v>
       </c>
       <c r="F126" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -8223,13 +8223,13 @@
         <v>0</v>
       </c>
       <c r="J126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K126" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M126" t="n">
         <v>0</v>
@@ -8270,10 +8270,10 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F127" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -8288,7 +8288,7 @@
         <v>3</v>
       </c>
       <c r="K127" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="L127" t="n">
         <v>1</v>
@@ -8332,10 +8332,10 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F128" t="n">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -8347,10 +8347,10 @@
         <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K128" t="n">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L128" t="n">
         <v>3</v>
@@ -8456,7 +8456,7 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F130" t="n">
         <v>176</v>
@@ -8471,10 +8471,10 @@
         <v>9</v>
       </c>
       <c r="J130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K130" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L130" t="n">
         <v>4</v>
@@ -8704,10 +8704,10 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="F134" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -8719,10 +8719,10 @@
         <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K134" t="n">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L134" t="n">
         <v>2</v>
@@ -9451,7 +9451,7 @@
         <v>23</v>
       </c>
       <c r="F146" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -9466,13 +9466,13 @@
         <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L146" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N146" t="inlineStr">
         <is>
@@ -9962,10 +9962,10 @@
         <v>1</v>
       </c>
       <c r="K154" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L154" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M154" t="n">
         <v>0</v>
@@ -10750,7 +10750,7 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F167" t="n">
         <v>32</v>
@@ -10765,10 +10765,10 @@
         <v>0</v>
       </c>
       <c r="J167" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K167" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="L167" t="n">
         <v>0</v>
@@ -10936,7 +10936,7 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="F170" t="n">
         <v>52</v>
@@ -10951,10 +10951,10 @@
         <v>0</v>
       </c>
       <c r="J170" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K170" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="L170" t="n">
         <v>0</v>
@@ -11060,25 +11060,25 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F172" t="n">
+        <v>2</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0</v>
+      </c>
+      <c r="H172" t="n">
+        <v>0</v>
+      </c>
+      <c r="I172" t="n">
+        <v>0</v>
+      </c>
+      <c r="J172" t="n">
+        <v>2</v>
+      </c>
+      <c r="K172" t="n">
         <v>4</v>
-      </c>
-      <c r="G172" t="n">
-        <v>0</v>
-      </c>
-      <c r="H172" t="n">
-        <v>0</v>
-      </c>
-      <c r="I172" t="n">
-        <v>0</v>
-      </c>
-      <c r="J172" t="n">
-        <v>1</v>
-      </c>
-      <c r="K172" t="n">
-        <v>5</v>
       </c>
       <c r="L172" t="n">
         <v>0</v>
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F173" t="n">
         <v>0</v>
@@ -11137,13 +11137,13 @@
         <v>0</v>
       </c>
       <c r="J173" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K173" t="n">
         <v>4</v>
       </c>
       <c r="L173" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M173" t="n">
         <v>1</v>
@@ -11184,10 +11184,10 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="F174" t="n">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="G174" t="n">
         <v>30</v>
@@ -11199,10 +11199,10 @@
         <v>1</v>
       </c>
       <c r="J174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K174" t="n">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="L174" t="n">
         <v>3</v>
@@ -11373,7 +11373,7 @@
         <v>15</v>
       </c>
       <c r="F177" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -11385,7 +11385,7 @@
         <v>0</v>
       </c>
       <c r="J177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K177" t="n">
         <v>16</v>
@@ -12070,10 +12070,10 @@
         <v>2</v>
       </c>
       <c r="K188" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M188" t="n">
         <v>0</v>
